--- a/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Defect_Log.xlsx
+++ b/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Defect_Log.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -89,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,7 +98,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -490,6 +492,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -558,7 +561,7 @@
           <t>D-01</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -618,7 +621,7 @@
           <t>D-02</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -653,17 +656,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Map startTime and endTime to start and end in loadSlots in BookSlot.jsx (3 lines). Fix proven in the test copy and not yet merged</t>
+          <t>Map startTime and endTime to start and end in loadSlots in BookSlot.jsx. Fix is in the working copy and not yet committed</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Pass in the test copy: 09:00 to 09:30 and 09:30 to 10:00 (TC-32). Repeat after the merge</t>
+          <t>Pass: 09:00 to 09:30 and 09:30 to 10:00 (TC-32)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -678,7 +681,7 @@
           <t>D-03</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -688,7 +691,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The page only says This page is coming soon so lecturers cannot publish edit or see slots from the app (FR-03 and FR-09)</t>
+          <t>The merged page does not work with the Slots API: it calls /api/slots/my but the route is /api/slots/mine so the list shows That API route does not exist and it sends start and end but the API needs startTime and endTime so publishing fails (FR-03 and FR-09)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -713,22 +716,22 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Build the page (Week 4 coding task 7) using the working slots API</t>
+          <t>Use /api/slots/mine and send startTime and endTime and map them when listing in LecturerSlots.jsx. Fix is in the working copy and not yet committed</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Not retested: TC-25 fails</t>
+          <t>Pass: the list shows the slots and publish and remove both work (TC-25 and TC-33)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>TC-25 and laptop_lecturer.png</t>
+          <t>TC-25 and TC-33 and D-03_fix_LecturerSlots.patch</t>
         </is>
       </c>
     </row>
@@ -738,7 +741,7 @@
           <t>D-04</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -773,17 +776,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Add a change button that picks a new slot and calls PATCH /api/bookings/:id/change</t>
+          <t>Added a Change time button on My bookings that lists the other open times of that lecturer and calls PATCH /api/bookings/:id/change. The bookings API now also returns lecturerId. Not yet committed</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Not retested: TC-29 fails</t>
+          <t>Pass: the booking moved and the notice showed (TC-29)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -798,7 +801,7 @@
           <t>D-05</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -833,17 +836,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Add a response interceptor in api.js that clears the saved login and goes to /login on a 401</t>
+          <t>Response interceptor in api.js clears the saved login and goes to /login with the message Your session has ended on a 401. Not yet committed</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Not retested: TC-28 fails</t>
+          <t>Pass (TC-28)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -858,7 +861,7 @@
           <t>D-06</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -893,17 +896,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Add rate limiting to POST /api/auth/login in the Week 5 security check</t>
+          <t>Login allows 10 wrong passwords per account and address in 15 minutes and then answers 429. Not yet committed</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Not retested: TC-30 fails</t>
+          <t>Pass: attempts 11 and 12 gave 429 and another account still logged in (TC-30)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -918,7 +921,7 @@
           <t>D-07</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -953,17 +956,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Change the text and the diagram label to every minute in the final dissertation</t>
+          <t>Chapter 4 text changed to every minute. The architecture diagram label should be checked in the final dissertation</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Not retested</t>
+          <t>Pass: the text matches jobs/reminders.js</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -978,7 +981,7 @@
           <t>D-08</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>46317</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1013,17 +1016,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Keep the confirm step visible after an error</t>
+          <t>The confirm step stays visible after an error unless the slot was taken. Not yet committed</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Not retested</t>
+          <t>Pass (TC-16b)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1035,76 +1038,122 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer slots page</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>The page can publish and remove slots but has no way to edit a slot although the API supports editing (FR-03)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Willem Gerber</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Thomas du Plessis</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Added an Edit button that fills the form and saves with PUT /api/slots/:id. Not yet committed</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Pass: the new location was saved (TC-34)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>D-09</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>46317</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Route protection</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>A logged in user who opens the other roles page is sent to the login page and not to their own home page</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Lebohang Tlaitlai</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Send the user to their own home page in ProtectedRoute</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Not retested</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ProtectedRoute sends the user to their own home page. Not yet committed</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Pass (TC-27)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>TC-27</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>

--- a/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Defect_Log.xlsx
+++ b/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Defect_Log.xlsx
@@ -492,7 +492,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -661,7 +660,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Map startTime and endTime to start and end in loadSlots in BookSlot.jsx. Fix is in the working copy and not yet committed</t>
+          <t>Map startTime and endTime to start and end in loadSlots in BookSlot.jsx. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +720,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Use /api/slots/mine and send startTime and endTime and map them when listing in LecturerSlots.jsx. Fix is in the working copy and not yet committed</t>
+          <t>Use /api/slots/mine and send startTime and endTime and map them when listing in LecturerSlots.jsx. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -731,7 +730,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>TC-25 and TC-33 and D-03_fix_LecturerSlots.patch</t>
+          <t>TC-25 and TC-33 and commit 09effbe</t>
         </is>
       </c>
     </row>
@@ -781,7 +780,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Added a Change time button on My bookings that lists the other open times of that lecturer and calls PATCH /api/bookings/:id/change. The bookings API now also returns lecturerId. Not yet committed</t>
+          <t>Added a Change time button on My bookings that lists the other open times of that lecturer and calls PATCH /api/bookings/:id/change. The bookings API now also returns lecturerId. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -841,7 +840,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Response interceptor in api.js clears the saved login and goes to /login with the message Your session has ended on a 401. Not yet committed</t>
+          <t>Response interceptor in api.js clears the saved login and goes to /login with the message Your session has ended on a 401. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -901,7 +900,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Login allows 10 wrong passwords per account and address in 15 minutes and then answers 429. Not yet committed</t>
+          <t>Login allows 10 wrong passwords per account and address in 15 minutes and then answers 429. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1021,7 +1020,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>The confirm step stays visible after an error unless the slot was taken. Not yet committed</t>
+          <t>The confirm step stays visible after an error unless the slot was taken. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1081,7 +1080,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Added an Edit button that fills the form and saves with PUT /api/slots/:id. Not yet committed</t>
+          <t>Added an Edit button that fills the form and saves with PUT /api/slots/:id. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1141,7 +1140,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>ProtectedRoute sends the user to their own home page. Not yet committed</t>
+          <t>ProtectedRoute sends the user to their own home page. Committed in 09effbe on 26 October 2026</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
